--- a/Data/notes.xlsx
+++ b/Data/notes.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11028"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FCF82B-F166-F340-8541-7DECDA2B0F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7F2DC9-C712-7549-B596-B7448127A3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1523,6 +1523,7 @@
       <sheetName val="Venues-test"/>
       <sheetName val="Venues-test2"/>
       <sheetName val="Venues-test3"/>
+      <sheetName val="Latest_Data"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -1530,6 +1531,7 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1601,14 +1603,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7239FA1E-6F6B-584D-901B-444008E177A4}" name="Table4" displayName="Table4" ref="A1:H294" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
-  <autoFilter ref="A1:H294" xr:uid="{7239FA1E-6F6B-584D-901B-444008E177A4}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ME 316"/>
-        <filter val="CS 303"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H294" xr:uid="{7239FA1E-6F6B-584D-901B-444008E177A4}"/>
   <tableColumns count="8">
     <tableColumn id="10" xr3:uid="{C8920EB4-755E-954E-99BA-8863FB4C0389}" name="Day" dataDxfId="8"/>
     <tableColumn id="1" xr3:uid="{BD582D4E-F965-9346-AA92-184D109C1C16}" name="Code" dataDxfId="7"/>
@@ -53078,7 +53073,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>310</v>
       </c>
@@ -53101,13 +53096,13 @@
       <c r="G2" s="19">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>310</v>
       </c>
@@ -53130,10 +53125,10 @@
       <c r="G3" s="19">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
@@ -53159,13 +53154,13 @@
       <c r="G4" s="19">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>310</v>
       </c>
@@ -53188,13 +53183,13 @@
       <c r="G5" s="19">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>310</v>
       </c>
@@ -53217,13 +53212,13 @@
       <c r="G6" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>310</v>
       </c>
@@ -53246,13 +53241,13 @@
       <c r="G7" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>310</v>
       </c>
@@ -53275,13 +53270,13 @@
       <c r="G8" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>310</v>
       </c>
@@ -53304,10 +53299,10 @@
       <c r="G9" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J9" s="17" t="s">
         <v>202</v>
@@ -53335,10 +53330,10 @@
       <c r="G10" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
@@ -53363,10 +53358,10 @@
       <c r="G11" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
@@ -53391,13 +53386,13 @@
       <c r="G12" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>310</v>
       </c>
@@ -53420,13 +53415,13 @@
       <c r="G13" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>310</v>
       </c>
@@ -53449,13 +53444,13 @@
       <c r="G14" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>310</v>
       </c>
@@ -53478,13 +53473,13 @@
       <c r="G15" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>310</v>
       </c>
@@ -53507,13 +53502,13 @@
       <c r="G16" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>310</v>
       </c>
@@ -53535,13 +53530,13 @@
       <c r="G17" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>310</v>
       </c>
@@ -53563,13 +53558,13 @@
       <c r="G18" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>310</v>
       </c>
@@ -53591,13 +53586,13 @@
       <c r="G19" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>310</v>
       </c>
@@ -53620,13 +53615,13 @@
       <c r="G20" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>310</v>
       </c>
@@ -53649,13 +53644,13 @@
       <c r="G21" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>310</v>
       </c>
@@ -53678,13 +53673,13 @@
       <c r="G22" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>310</v>
       </c>
@@ -53706,13 +53701,13 @@
       <c r="G23" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>310</v>
       </c>
@@ -53734,13 +53729,13 @@
       <c r="G24" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>310</v>
       </c>
@@ -53762,13 +53757,13 @@
       <c r="G25" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>310</v>
       </c>
@@ -53791,13 +53786,13 @@
       <c r="G26" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>310</v>
       </c>
@@ -53820,13 +53815,13 @@
       <c r="G27" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>310</v>
       </c>
@@ -53849,13 +53844,13 @@
       <c r="G28" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>310</v>
       </c>
@@ -53877,13 +53872,13 @@
       <c r="G29" s="19">
         <v>0.5</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>310</v>
       </c>
@@ -53905,13 +53900,13 @@
       <c r="G30" s="19">
         <v>0.5</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>310</v>
       </c>
@@ -53934,13 +53929,13 @@
       <c r="G31" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>310</v>
       </c>
@@ -53963,13 +53958,13 @@
       <c r="G32" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>310</v>
       </c>
@@ -53992,13 +53987,13 @@
       <c r="G33" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>310</v>
       </c>
@@ -54021,13 +54016,13 @@
       <c r="G34" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>310</v>
       </c>
@@ -54050,13 +54045,13 @@
       <c r="G35" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>310</v>
       </c>
@@ -54079,13 +54074,13 @@
       <c r="G36" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>310</v>
       </c>
@@ -54108,13 +54103,13 @@
       <c r="G37" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
         <v>310</v>
       </c>
@@ -54137,13 +54132,13 @@
       <c r="G38" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>310</v>
       </c>
@@ -54166,13 +54161,13 @@
       <c r="G39" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>310</v>
       </c>
@@ -54194,13 +54189,13 @@
       <c r="G40" s="19">
         <v>0.66666666666666674</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>310</v>
       </c>
@@ -54222,13 +54217,13 @@
       <c r="G41" s="19">
         <v>0.66666666666666674</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>310</v>
       </c>
@@ -54250,13 +54245,13 @@
       <c r="G42" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>310</v>
       </c>
@@ -54278,13 +54273,13 @@
       <c r="G43" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>310</v>
       </c>
@@ -54306,13 +54301,13 @@
       <c r="G44" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>310</v>
       </c>
@@ -54335,13 +54330,13 @@
       <c r="G45" s="19">
         <v>0.625</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
         <v>310</v>
       </c>
@@ -54364,13 +54359,13 @@
       <c r="G46" s="19">
         <v>0.625</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>310</v>
       </c>
@@ -54393,13 +54388,13 @@
       <c r="G47" s="19">
         <v>0.625</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
         <v>310</v>
       </c>
@@ -54421,13 +54416,13 @@
       <c r="G48" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>310</v>
       </c>
@@ -54449,13 +54444,13 @@
       <c r="G49" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
         <v>310</v>
       </c>
@@ -54477,13 +54472,13 @@
       <c r="G50" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H50" s="18">
+      <c r="H50" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>310</v>
       </c>
@@ -54505,13 +54500,13 @@
       <c r="G51" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H51" s="18">
+      <c r="H51" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
         <v>310</v>
       </c>
@@ -54533,13 +54528,13 @@
       <c r="G52" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H52" s="18">
+      <c r="H52" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>310</v>
       </c>
@@ -54561,13 +54556,13 @@
       <c r="G53" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H53" s="18">
+      <c r="H53" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
         <v>310</v>
       </c>
@@ -54589,13 +54584,13 @@
       <c r="G54" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H54" s="18">
+      <c r="H54" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>310</v>
       </c>
@@ -54617,13 +54612,13 @@
       <c r="G55" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H55" s="18">
+      <c r="H55" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
         <v>310</v>
       </c>
@@ -54645,13 +54640,13 @@
       <c r="G56" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H56" s="18">
+      <c r="H56" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>310</v>
       </c>
@@ -54674,13 +54669,13 @@
       <c r="G57" s="19">
         <v>0.625</v>
       </c>
-      <c r="H57" s="18">
+      <c r="H57" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
         <v>310</v>
       </c>
@@ -54702,13 +54697,13 @@
       <c r="G58" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H58" s="18">
+      <c r="H58" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
         <v>310</v>
       </c>
@@ -54730,13 +54725,13 @@
       <c r="G59" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H59" s="18">
+      <c r="H59" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
         <v>310</v>
       </c>
@@ -54758,13 +54753,13 @@
       <c r="G60" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H60" s="18">
+      <c r="H60" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>310</v>
       </c>
@@ -54787,13 +54782,13 @@
       <c r="G61" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H61" s="18">
+      <c r="H61" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>310</v>
       </c>
@@ -54816,13 +54811,13 @@
       <c r="G62" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H62" s="18">
+      <c r="H62" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>310</v>
       </c>
@@ -54845,13 +54840,13 @@
       <c r="G63" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H63" s="18">
+      <c r="H63" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>310</v>
       </c>
@@ -54874,13 +54869,13 @@
       <c r="G64" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H64" s="18">
+      <c r="H64" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>310</v>
       </c>
@@ -54903,13 +54898,13 @@
       <c r="G65" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H65" s="18">
+      <c r="H65" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>310</v>
       </c>
@@ -54932,13 +54927,13 @@
       <c r="G66" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H66" s="18">
+      <c r="H66" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>310</v>
       </c>
@@ -54961,13 +54956,13 @@
       <c r="G67" s="19">
         <v>0.75</v>
       </c>
-      <c r="H67" s="18">
+      <c r="H67" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>310</v>
       </c>
@@ -54990,13 +54985,13 @@
       <c r="G68" s="19">
         <v>0.75</v>
       </c>
-      <c r="H68" s="18">
+      <c r="H68" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>310</v>
       </c>
@@ -55019,13 +55014,13 @@
       <c r="G69" s="19">
         <v>0.75</v>
       </c>
-      <c r="H69" s="18">
+      <c r="H69" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
         <v>316</v>
       </c>
@@ -55048,13 +55043,13 @@
       <c r="G70" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H70" s="18">
+      <c r="H70" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
         <v>316</v>
       </c>
@@ -55077,13 +55072,13 @@
       <c r="G71" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H71" s="18">
+      <c r="H71" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
         <v>316</v>
       </c>
@@ -55106,13 +55101,13 @@
       <c r="G72" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H72" s="18">
+      <c r="H72" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
         <v>316</v>
       </c>
@@ -55135,13 +55130,13 @@
       <c r="G73" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H73" s="18">
+      <c r="H73" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
         <v>316</v>
       </c>
@@ -55164,13 +55159,13 @@
       <c r="G74" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H74" s="18">
+      <c r="H74" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
         <v>316</v>
       </c>
@@ -55193,13 +55188,13 @@
       <c r="G75" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H75" s="18">
+      <c r="H75" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="20" t="s">
         <v>316</v>
       </c>
@@ -55222,13 +55217,13 @@
       <c r="G76" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H76" s="18">
+      <c r="H76" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20" t="s">
         <v>316</v>
       </c>
@@ -55250,13 +55245,13 @@
       <c r="G77" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H77" s="18">
+      <c r="H77" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20" t="s">
         <v>316</v>
       </c>
@@ -55278,13 +55273,13 @@
       <c r="G78" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H78" s="18">
+      <c r="H78" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20" t="s">
         <v>316</v>
       </c>
@@ -55306,13 +55301,13 @@
       <c r="G79" s="19">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H79" s="18">
+      <c r="H79" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="20" t="s">
         <v>316</v>
       </c>
@@ -55334,13 +55329,13 @@
       <c r="G80" s="19">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H80" s="18">
+      <c r="H80" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
         <v>316</v>
       </c>
@@ -55363,13 +55358,13 @@
       <c r="G81" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H81" s="18">
+      <c r="H81" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="20" t="s">
         <v>316</v>
       </c>
@@ -55391,13 +55386,13 @@
       <c r="G82" s="19">
         <v>0.5</v>
       </c>
-      <c r="H82" s="18">
+      <c r="H82" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="20" t="s">
         <v>316</v>
       </c>
@@ -55419,13 +55414,13 @@
       <c r="G83" s="19">
         <v>0.5</v>
       </c>
-      <c r="H83" s="18">
+      <c r="H83" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="20" t="s">
         <v>316</v>
       </c>
@@ -55448,13 +55443,13 @@
       <c r="G84" s="19">
         <v>0.625</v>
       </c>
-      <c r="H84" s="18">
+      <c r="H84" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="20" t="s">
         <v>316</v>
       </c>
@@ -55477,13 +55472,13 @@
       <c r="G85" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H85" s="18">
+      <c r="H85" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
         <v>316</v>
       </c>
@@ -55506,13 +55501,13 @@
       <c r="G86" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H86" s="18">
+      <c r="H86" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="20" t="s">
         <v>316</v>
       </c>
@@ -55535,13 +55530,13 @@
       <c r="G87" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H87" s="18">
+      <c r="H87" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="20" t="s">
         <v>316</v>
       </c>
@@ -55564,13 +55559,13 @@
       <c r="G88" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H88" s="18">
+      <c r="H88" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="20" t="s">
         <v>316</v>
       </c>
@@ -55593,13 +55588,13 @@
       <c r="G89" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H89" s="18">
+      <c r="H89" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="20" t="s">
         <v>316</v>
       </c>
@@ -55621,13 +55616,13 @@
       <c r="G90" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H90" s="18">
+      <c r="H90" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="20" t="s">
         <v>316</v>
       </c>
@@ -55649,13 +55644,13 @@
       <c r="G91" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H91" s="18">
+      <c r="H91" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20" t="s">
         <v>316</v>
       </c>
@@ -55678,13 +55673,13 @@
       <c r="G92" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H92" s="18">
+      <c r="H92" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="20" t="s">
         <v>316</v>
       </c>
@@ -55707,13 +55702,13 @@
       <c r="G93" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H93" s="18">
+      <c r="H93" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="20" t="s">
         <v>316</v>
       </c>
@@ -55736,13 +55731,13 @@
       <c r="G94" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H94" s="18">
+      <c r="H94" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="20" t="s">
         <v>316</v>
       </c>
@@ -55765,13 +55760,13 @@
       <c r="G95" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H95" s="18">
+      <c r="H95" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="20" t="s">
         <v>316</v>
       </c>
@@ -55794,13 +55789,13 @@
       <c r="G96" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H96" s="18">
+      <c r="H96" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="20" t="s">
         <v>316</v>
       </c>
@@ -55823,13 +55818,13 @@
       <c r="G97" s="19">
         <v>0.625</v>
       </c>
-      <c r="H97" s="18">
+      <c r="H97" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="20" t="s">
         <v>316</v>
       </c>
@@ -55852,13 +55847,13 @@
       <c r="G98" s="19">
         <v>0.75</v>
       </c>
-      <c r="H98" s="18">
+      <c r="H98" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="20" t="s">
         <v>316</v>
       </c>
@@ -55881,13 +55876,13 @@
       <c r="G99" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H99" s="18">
+      <c r="H99" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="20" t="s">
         <v>316</v>
       </c>
@@ -55910,13 +55905,13 @@
       <c r="G100" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H100" s="18">
+      <c r="H100" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
         <v>316</v>
       </c>
@@ -55939,13 +55934,13 @@
       <c r="G101" s="19">
         <v>0.75</v>
       </c>
-      <c r="H101" s="18">
+      <c r="H101" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="20" t="s">
         <v>316</v>
       </c>
@@ -55968,13 +55963,13 @@
       <c r="G102" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H102" s="18">
+      <c r="H102" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="20" t="s">
         <v>316</v>
       </c>
@@ -55997,13 +55992,13 @@
       <c r="G103" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H103" s="18">
+      <c r="H103" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="20" t="s">
         <v>316</v>
       </c>
@@ -56025,13 +56020,13 @@
       <c r="G104" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H104" s="18">
+      <c r="H104" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="20" t="s">
         <v>316</v>
       </c>
@@ -56053,13 +56048,13 @@
       <c r="G105" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H105" s="18">
+      <c r="H105" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="20" t="s">
         <v>316</v>
       </c>
@@ -56082,13 +56077,13 @@
       <c r="G106" s="19">
         <v>0.625</v>
       </c>
-      <c r="H106" s="18">
+      <c r="H106" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="20" t="s">
         <v>316</v>
       </c>
@@ -56111,13 +56106,13 @@
       <c r="G107" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H107" s="18">
+      <c r="H107" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="20" t="s">
         <v>316</v>
       </c>
@@ -56140,13 +56135,13 @@
       <c r="G108" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H108" s="18">
+      <c r="H108" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="20" t="s">
         <v>316</v>
       </c>
@@ -56169,13 +56164,13 @@
       <c r="G109" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H109" s="18">
+      <c r="H109" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20" t="s">
         <v>316</v>
       </c>
@@ -56198,13 +56193,13 @@
       <c r="G110" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H110" s="18">
+      <c r="H110" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20" t="s">
         <v>316</v>
       </c>
@@ -56227,13 +56222,13 @@
       <c r="G111" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H111" s="18">
+      <c r="H111" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20" t="s">
         <v>316</v>
       </c>
@@ -56256,13 +56251,13 @@
       <c r="G112" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H112" s="18">
+      <c r="H112" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
         <v>316</v>
       </c>
@@ -56285,13 +56280,13 @@
       <c r="G113" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H113" s="18">
+      <c r="H113" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="20" t="s">
         <v>316</v>
       </c>
@@ -56314,13 +56309,13 @@
       <c r="G114" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H114" s="18">
+      <c r="H114" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="20" t="s">
         <v>316</v>
       </c>
@@ -56342,16 +56337,16 @@
       <c r="G115" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H115" s="18">
+      <c r="H115" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J115" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20" t="s">
         <v>316</v>
       </c>
@@ -56373,16 +56368,16 @@
       <c r="G116" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H116" s="18">
+      <c r="H116" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J116" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="20" t="s">
         <v>316</v>
       </c>
@@ -56404,16 +56399,16 @@
       <c r="G117" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H117" s="18">
+      <c r="H117" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J117" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="20" t="s">
         <v>316</v>
       </c>
@@ -56436,13 +56431,13 @@
       <c r="G118" s="19">
         <v>0.75</v>
       </c>
-      <c r="H118" s="18">
+      <c r="H118" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20" t="s">
         <v>316</v>
       </c>
@@ -56465,13 +56460,13 @@
       <c r="G119" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H119" s="18">
+      <c r="H119" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="20" t="s">
         <v>316</v>
       </c>
@@ -56494,13 +56489,13 @@
       <c r="G120" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H120" s="18">
+      <c r="H120" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="20" t="s">
         <v>316</v>
       </c>
@@ -56523,13 +56518,13 @@
       <c r="G121" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H121" s="18">
+      <c r="H121" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="20" t="s">
         <v>316</v>
       </c>
@@ -56552,13 +56547,13 @@
       <c r="G122" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H122" s="18">
+      <c r="H122" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="20" t="s">
         <v>316</v>
       </c>
@@ -56581,13 +56576,13 @@
       <c r="G123" s="19">
         <v>0.75</v>
       </c>
-      <c r="H123" s="18">
+      <c r="H123" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="20" t="s">
         <v>316</v>
       </c>
@@ -56610,13 +56605,13 @@
       <c r="G124" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H124" s="18">
+      <c r="H124" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
         <v>316</v>
       </c>
@@ -56638,13 +56633,13 @@
       <c r="G125" s="19">
         <v>0.75</v>
       </c>
-      <c r="H125" s="18">
+      <c r="H125" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20" t="s">
         <v>316</v>
       </c>
@@ -56666,13 +56661,13 @@
       <c r="G126" s="19">
         <v>0.75</v>
       </c>
-      <c r="H126" s="18">
+      <c r="H126" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20" t="s">
         <v>316</v>
       </c>
@@ -56694,13 +56689,13 @@
       <c r="G127" s="19">
         <v>0.75</v>
       </c>
-      <c r="H127" s="18">
+      <c r="H127" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20" t="s">
         <v>316</v>
       </c>
@@ -56722,13 +56717,13 @@
       <c r="G128" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H128" s="18">
+      <c r="H128" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20" t="s">
         <v>316</v>
       </c>
@@ -56750,13 +56745,13 @@
       <c r="G129" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H129" s="18">
+      <c r="H129" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20" t="s">
         <v>316</v>
       </c>
@@ -56778,13 +56773,13 @@
       <c r="G130" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H130" s="18">
+      <c r="H130" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20" t="s">
         <v>316</v>
       </c>
@@ -56807,13 +56802,13 @@
       <c r="G131" s="19">
         <v>0.75</v>
       </c>
-      <c r="H131" s="18">
+      <c r="H131" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="20" t="s">
         <v>316</v>
       </c>
@@ -56836,13 +56831,13 @@
       <c r="G132" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H132" s="18">
+      <c r="H132" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="20" t="s">
         <v>317</v>
       </c>
@@ -56865,13 +56860,13 @@
       <c r="G133" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H133" s="18">
+      <c r="H133" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="20" t="s">
         <v>317</v>
       </c>
@@ -56894,13 +56889,13 @@
       <c r="G134" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H134" s="18">
+      <c r="H134" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="20" t="s">
         <v>317</v>
       </c>
@@ -56923,13 +56918,13 @@
       <c r="G135" s="19">
         <v>0.625</v>
       </c>
-      <c r="H135" s="18">
+      <c r="H135" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="s">
         <v>317</v>
       </c>
@@ -56951,13 +56946,13 @@
       <c r="G136" s="19">
         <v>0.66666666666666674</v>
       </c>
-      <c r="H136" s="18">
+      <c r="H136" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="s">
         <v>317</v>
       </c>
@@ -56979,13 +56974,13 @@
       <c r="G137" s="19">
         <v>0.66666666666666674</v>
       </c>
-      <c r="H137" s="18">
+      <c r="H137" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="s">
         <v>317</v>
       </c>
@@ -57008,13 +57003,13 @@
       <c r="G138" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H138" s="18">
+      <c r="H138" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="20" t="s">
         <v>317</v>
       </c>
@@ -57037,13 +57032,13 @@
       <c r="G139" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H139" s="18">
+      <c r="H139" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="20" t="s">
         <v>317</v>
       </c>
@@ -57066,13 +57061,13 @@
       <c r="G140" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H140" s="18">
+      <c r="H140" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="20" t="s">
         <v>317</v>
       </c>
@@ -57095,13 +57090,13 @@
       <c r="G141" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H141" s="18">
+      <c r="H141" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="20" t="s">
         <v>317</v>
       </c>
@@ -57124,13 +57119,13 @@
       <c r="G142" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H142" s="18">
+      <c r="H142" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="20" t="s">
         <v>317</v>
       </c>
@@ -57153,13 +57148,13 @@
       <c r="G143" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H143" s="18">
+      <c r="H143" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20" t="s">
         <v>317</v>
       </c>
@@ -57182,13 +57177,13 @@
       <c r="G144" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H144" s="18">
+      <c r="H144" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="20" t="s">
         <v>317</v>
       </c>
@@ -57211,13 +57206,13 @@
       <c r="G145" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H145" s="18">
+      <c r="H145" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="s">
         <v>317</v>
       </c>
@@ -57239,13 +57234,13 @@
       <c r="G146" s="19">
         <v>0.75</v>
       </c>
-      <c r="H146" s="18">
+      <c r="H146" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="20" t="s">
         <v>317</v>
       </c>
@@ -57267,13 +57262,13 @@
       <c r="G147" s="19">
         <v>0.75</v>
       </c>
-      <c r="H147" s="18">
+      <c r="H147" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="s">
         <v>317</v>
       </c>
@@ -57295,13 +57290,13 @@
       <c r="G148" s="19">
         <v>0.75</v>
       </c>
-      <c r="H148" s="18">
+      <c r="H148" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="20" t="s">
         <v>317</v>
       </c>
@@ -57324,10 +57319,10 @@
       <c r="G149" s="19">
         <v>0.625</v>
       </c>
-      <c r="H149" s="18">
+      <c r="H149" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
@@ -57353,13 +57348,13 @@
       <c r="G150" s="19">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H150" s="18">
+      <c r="H150" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="20" t="s">
         <v>317</v>
       </c>
@@ -57381,13 +57376,13 @@
       <c r="G151" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H151" s="18">
+      <c r="H151" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20" t="s">
         <v>317</v>
       </c>
@@ -57409,13 +57404,13 @@
       <c r="G152" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H152" s="18">
+      <c r="H152" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="20" t="s">
         <v>317</v>
       </c>
@@ -57437,13 +57432,13 @@
       <c r="G153" s="19">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H153" s="18">
+      <c r="H153" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20" t="s">
         <v>317</v>
       </c>
@@ -57466,13 +57461,13 @@
       <c r="G154" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H154" s="18">
+      <c r="H154" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="20" t="s">
         <v>317</v>
       </c>
@@ -57495,13 +57490,13 @@
       <c r="G155" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H155" s="18">
+      <c r="H155" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="20" t="s">
         <v>317</v>
       </c>
@@ -57524,13 +57519,13 @@
       <c r="G156" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H156" s="18">
+      <c r="H156" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="20" t="s">
         <v>317</v>
       </c>
@@ -57552,13 +57547,13 @@
       <c r="G157" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H157" s="18">
+      <c r="H157" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20" t="s">
         <v>317</v>
       </c>
@@ -57580,13 +57575,13 @@
       <c r="G158" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H158" s="18">
+      <c r="H158" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="20" t="s">
         <v>317</v>
       </c>
@@ -57608,13 +57603,13 @@
       <c r="G159" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H159" s="18">
+      <c r="H159" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="20" t="s">
         <v>317</v>
       </c>
@@ -57637,13 +57632,13 @@
       <c r="G160" s="19">
         <v>0.625</v>
       </c>
-      <c r="H160" s="18">
+      <c r="H160" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="20" t="s">
         <v>317</v>
       </c>
@@ -57666,13 +57661,13 @@
       <c r="G161" s="19">
         <v>0.625</v>
       </c>
-      <c r="H161" s="18">
+      <c r="H161" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20" t="s">
         <v>317</v>
       </c>
@@ -57695,13 +57690,13 @@
       <c r="G162" s="19">
         <v>0.75</v>
       </c>
-      <c r="H162" s="18">
+      <c r="H162" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20" t="s">
         <v>317</v>
       </c>
@@ -57724,13 +57719,13 @@
       <c r="G163" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H163" s="18">
+      <c r="H163" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20" t="s">
         <v>317</v>
       </c>
@@ -57753,13 +57748,13 @@
       <c r="G164" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H164" s="18">
+      <c r="H164" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="20" t="s">
         <v>317</v>
       </c>
@@ -57782,13 +57777,13 @@
       <c r="G165" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H165" s="18">
+      <c r="H165" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="20" t="s">
         <v>317</v>
       </c>
@@ -57811,13 +57806,13 @@
       <c r="G166" s="19">
         <v>0.625</v>
       </c>
-      <c r="H166" s="18">
+      <c r="H166" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="20" t="s">
         <v>317</v>
       </c>
@@ -57840,13 +57835,13 @@
       <c r="G167" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H167" s="18">
+      <c r="H167" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20" t="s">
         <v>317</v>
       </c>
@@ -57869,13 +57864,13 @@
       <c r="G168" s="19">
         <v>0.625</v>
       </c>
-      <c r="H168" s="18">
+      <c r="H168" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="20" t="s">
         <v>317</v>
       </c>
@@ -57898,13 +57893,13 @@
       <c r="G169" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H169" s="18">
+      <c r="H169" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="20" t="s">
         <v>317</v>
       </c>
@@ -57927,13 +57922,13 @@
       <c r="G170" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H170" s="18">
+      <c r="H170" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="20" t="s">
         <v>317</v>
       </c>
@@ -57956,13 +57951,13 @@
       <c r="G171" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H171" s="18">
+      <c r="H171" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="s">
         <v>317</v>
       </c>
@@ -57985,13 +57980,13 @@
       <c r="G172" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H172" s="18">
+      <c r="H172" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="20" t="s">
         <v>317</v>
       </c>
@@ -58014,13 +58009,13 @@
       <c r="G173" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H173" s="18">
+      <c r="H173" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="20" t="s">
         <v>317</v>
       </c>
@@ -58043,13 +58038,13 @@
       <c r="G174" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H174" s="18">
+      <c r="H174" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="20" t="s">
         <v>317</v>
       </c>
@@ -58072,13 +58067,13 @@
       <c r="G175" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H175" s="18">
+      <c r="H175" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="s">
         <v>317</v>
       </c>
@@ -58101,13 +58096,13 @@
       <c r="G176" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H176" s="18">
+      <c r="H176" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20" t="s">
         <v>317</v>
       </c>
@@ -58130,13 +58125,13 @@
       <c r="G177" s="19">
         <v>0.75</v>
       </c>
-      <c r="H177" s="18">
+      <c r="H177" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20" t="s">
         <v>317</v>
       </c>
@@ -58159,13 +58154,13 @@
       <c r="G178" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H178" s="18">
+      <c r="H178" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="20" t="s">
         <v>317</v>
       </c>
@@ -58188,16 +58183,16 @@
       <c r="G179" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H179" s="18">
+      <c r="H179" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J179" s="17" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20" t="s">
         <v>317</v>
       </c>
@@ -58220,13 +58215,13 @@
       <c r="G180" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H180" s="18">
+      <c r="H180" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="20" t="s">
         <v>317</v>
       </c>
@@ -58249,13 +58244,13 @@
       <c r="G181" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H181" s="18">
+      <c r="H181" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="20" t="s">
         <v>317</v>
       </c>
@@ -58278,13 +58273,13 @@
       <c r="G182" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H182" s="18">
+      <c r="H182" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="20" t="s">
         <v>317</v>
       </c>
@@ -58307,13 +58302,13 @@
       <c r="G183" s="19">
         <v>0.625</v>
       </c>
-      <c r="H183" s="18">
+      <c r="H183" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20" t="s">
         <v>317</v>
       </c>
@@ -58336,13 +58331,13 @@
       <c r="G184" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H184" s="18">
+      <c r="H184" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="20" t="s">
         <v>317</v>
       </c>
@@ -58365,13 +58360,13 @@
       <c r="G185" s="19">
         <v>0.625</v>
       </c>
-      <c r="H185" s="18">
+      <c r="H185" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="20" t="s">
         <v>317</v>
       </c>
@@ -58394,13 +58389,13 @@
       <c r="G186" s="19">
         <v>0.75</v>
       </c>
-      <c r="H186" s="18">
+      <c r="H186" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="20" t="s">
         <v>317</v>
       </c>
@@ -58423,13 +58418,13 @@
       <c r="G187" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H187" s="18">
+      <c r="H187" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="20" t="s">
         <v>317</v>
       </c>
@@ -58452,13 +58447,13 @@
       <c r="G188" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H188" s="18">
+      <c r="H188" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="20" t="s">
         <v>317</v>
       </c>
@@ -58481,13 +58476,13 @@
       <c r="G189" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H189" s="18">
+      <c r="H189" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20" t="s">
         <v>317</v>
       </c>
@@ -58509,13 +58504,13 @@
       <c r="G190" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H190" s="18">
+      <c r="H190" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="20" t="s">
         <v>317</v>
       </c>
@@ -58537,13 +58532,13 @@
       <c r="G191" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H191" s="18">
+      <c r="H191" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="20" t="s">
         <v>317</v>
       </c>
@@ -58565,13 +58560,13 @@
       <c r="G192" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H192" s="18">
+      <c r="H192" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="20" t="s">
         <v>317</v>
       </c>
@@ -58594,13 +58589,13 @@
       <c r="G193" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H193" s="18">
+      <c r="H193" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="20" t="s">
         <v>317</v>
       </c>
@@ -58623,13 +58618,13 @@
       <c r="G194" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H194" s="18">
+      <c r="H194" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="20" t="s">
         <v>317</v>
       </c>
@@ -58652,13 +58647,13 @@
       <c r="G195" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H195" s="18">
+      <c r="H195" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="20" t="s">
         <v>317</v>
       </c>
@@ -58681,13 +58676,13 @@
       <c r="G196" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H196" s="18">
+      <c r="H196" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="20" t="s">
         <v>318</v>
       </c>
@@ -58710,13 +58705,13 @@
       <c r="G197" s="19">
         <v>0.625</v>
       </c>
-      <c r="H197" s="18">
+      <c r="H197" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20" t="s">
         <v>318</v>
       </c>
@@ -58739,13 +58734,13 @@
       <c r="G198" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H198" s="18">
+      <c r="H198" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="20" t="s">
         <v>318</v>
       </c>
@@ -58768,13 +58763,13 @@
       <c r="G199" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H199" s="18">
+      <c r="H199" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20" t="s">
         <v>318</v>
       </c>
@@ -58796,13 +58791,13 @@
       <c r="G200" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H200" s="18">
+      <c r="H200" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="20" t="s">
         <v>318</v>
       </c>
@@ -58824,13 +58819,13 @@
       <c r="G201" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H201" s="18">
+      <c r="H201" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="20" t="s">
         <v>318</v>
       </c>
@@ -58852,13 +58847,13 @@
       <c r="G202" s="19">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H202" s="18">
+      <c r="H202" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="20" t="s">
         <v>318</v>
       </c>
@@ -58880,13 +58875,13 @@
       <c r="G203" s="19">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H203" s="18">
+      <c r="H203" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="20" t="s">
         <v>318</v>
       </c>
@@ -58909,13 +58904,13 @@
       <c r="G204" s="19">
         <v>0.75</v>
       </c>
-      <c r="H204" s="18">
+      <c r="H204" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="20" t="s">
         <v>318</v>
       </c>
@@ -58938,13 +58933,13 @@
       <c r="G205" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H205" s="18">
+      <c r="H205" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="20" t="s">
         <v>318</v>
       </c>
@@ -58967,13 +58962,13 @@
       <c r="G206" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H206" s="18">
+      <c r="H206" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="20" t="s">
         <v>318</v>
       </c>
@@ -58996,13 +58991,13 @@
       <c r="G207" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H207" s="18">
+      <c r="H207" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="20" t="s">
         <v>318</v>
       </c>
@@ -59025,13 +59020,13 @@
       <c r="G208" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H208" s="18">
+      <c r="H208" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="20" t="s">
         <v>318</v>
       </c>
@@ -59054,13 +59049,13 @@
       <c r="G209" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H209" s="18">
+      <c r="H209" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="20" t="s">
         <v>318</v>
       </c>
@@ -59083,13 +59078,13 @@
       <c r="G210" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H210" s="18">
+      <c r="H210" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="20" t="s">
         <v>318</v>
       </c>
@@ -59112,13 +59107,13 @@
       <c r="G211" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H211" s="18">
+      <c r="H211" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="20" t="s">
         <v>318</v>
       </c>
@@ -59141,13 +59136,13 @@
       <c r="G212" s="19">
         <v>0.75</v>
       </c>
-      <c r="H212" s="18">
+      <c r="H212" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="20" t="s">
         <v>318</v>
       </c>
@@ -59170,13 +59165,13 @@
       <c r="G213" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H213" s="18">
+      <c r="H213" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="20" t="s">
         <v>318</v>
       </c>
@@ -59199,13 +59194,13 @@
       <c r="G214" s="19">
         <v>0.75</v>
       </c>
-      <c r="H214" s="18">
+      <c r="H214" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="20" t="s">
         <v>318</v>
       </c>
@@ -59228,13 +59223,13 @@
       <c r="G215" s="19">
         <v>0.625</v>
       </c>
-      <c r="H215" s="18">
+      <c r="H215" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="20" t="s">
         <v>318</v>
       </c>
@@ -59257,13 +59252,13 @@
       <c r="G216" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H216" s="18">
+      <c r="H216" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="20" t="s">
         <v>318</v>
       </c>
@@ -59286,13 +59281,13 @@
       <c r="G217" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H217" s="18">
+      <c r="H217" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20" t="s">
         <v>318</v>
       </c>
@@ -59315,13 +59310,13 @@
       <c r="G218" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H218" s="18">
+      <c r="H218" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="20" t="s">
         <v>318</v>
       </c>
@@ -59344,13 +59339,13 @@
       <c r="G219" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H219" s="18">
+      <c r="H219" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20" t="s">
         <v>318</v>
       </c>
@@ -59373,13 +59368,13 @@
       <c r="G220" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H220" s="18">
+      <c r="H220" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20" t="s">
         <v>318</v>
       </c>
@@ -59402,13 +59397,13 @@
       <c r="G221" s="19">
         <v>0.75</v>
       </c>
-      <c r="H221" s="18">
+      <c r="H221" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="s">
         <v>318</v>
       </c>
@@ -59431,13 +59426,13 @@
       <c r="G222" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H222" s="18">
+      <c r="H222" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20" t="s">
         <v>318</v>
       </c>
@@ -59460,13 +59455,13 @@
       <c r="G223" s="19">
         <v>0.75</v>
       </c>
-      <c r="H223" s="18">
+      <c r="H223" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="s">
         <v>318</v>
       </c>
@@ -59488,13 +59483,13 @@
       <c r="G224" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H224" s="18">
+      <c r="H224" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20" t="s">
         <v>318</v>
       </c>
@@ -59516,13 +59511,13 @@
       <c r="G225" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H225" s="18">
+      <c r="H225" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20" t="s">
         <v>318</v>
       </c>
@@ -59545,13 +59540,13 @@
       <c r="G226" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H226" s="18">
+      <c r="H226" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="20" t="s">
         <v>318</v>
       </c>
@@ -59574,13 +59569,13 @@
       <c r="G227" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H227" s="18">
+      <c r="H227" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20" t="s">
         <v>318</v>
       </c>
@@ -59603,13 +59598,13 @@
       <c r="G228" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H228" s="18">
+      <c r="H228" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="20" t="s">
         <v>318</v>
       </c>
@@ -59632,13 +59627,13 @@
       <c r="G229" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H229" s="18">
+      <c r="H229" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20" t="s">
         <v>318</v>
       </c>
@@ -59661,13 +59656,13 @@
       <c r="G230" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H230" s="18">
+      <c r="H230" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20" t="s">
         <v>318</v>
       </c>
@@ -59690,13 +59685,13 @@
       <c r="G231" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H231" s="18">
+      <c r="H231" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20" t="s">
         <v>318</v>
       </c>
@@ -59718,13 +59713,13 @@
       <c r="G232" s="19">
         <v>0.46527777777777773</v>
       </c>
-      <c r="H232" s="18">
+      <c r="H232" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20" t="s">
         <v>318</v>
       </c>
@@ -59746,13 +59741,13 @@
       <c r="G233" s="19">
         <v>0.46527777777777773</v>
       </c>
-      <c r="H233" s="18">
+      <c r="H233" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20" t="s">
         <v>318</v>
       </c>
@@ -59774,13 +59769,13 @@
       <c r="G234" s="19">
         <v>0.46527777777777773</v>
       </c>
-      <c r="H234" s="18">
+      <c r="H234" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="20" t="s">
         <v>318</v>
       </c>
@@ -59803,13 +59798,13 @@
       <c r="G235" s="19">
         <v>0.625</v>
       </c>
-      <c r="H235" s="18">
+      <c r="H235" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20" t="s">
         <v>318</v>
       </c>
@@ -59831,13 +59826,13 @@
       <c r="G236" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H236" s="18">
+      <c r="H236" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20" t="s">
         <v>318</v>
       </c>
@@ -59859,13 +59854,13 @@
       <c r="G237" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H237" s="18">
+      <c r="H237" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20" t="s">
         <v>318</v>
       </c>
@@ -59887,13 +59882,13 @@
       <c r="G238" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H238" s="18">
+      <c r="H238" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20" t="s">
         <v>318</v>
       </c>
@@ -59916,13 +59911,13 @@
       <c r="G239" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H239" s="18">
+      <c r="H239" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20" t="s">
         <v>318</v>
       </c>
@@ -59945,13 +59940,13 @@
       <c r="G240" s="19">
         <v>0.75</v>
       </c>
-      <c r="H240" s="18">
+      <c r="H240" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20" t="s">
         <v>318</v>
       </c>
@@ -59974,13 +59969,13 @@
       <c r="G241" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H241" s="18">
+      <c r="H241" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20" t="s">
         <v>318</v>
       </c>
@@ -60003,13 +59998,13 @@
       <c r="G242" s="19">
         <v>0.75</v>
       </c>
-      <c r="H242" s="18">
+      <c r="H242" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20" t="s">
         <v>318</v>
       </c>
@@ -60032,13 +60027,13 @@
       <c r="G243" s="19">
         <v>0.625</v>
       </c>
-      <c r="H243" s="18">
+      <c r="H243" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20" t="s">
         <v>318</v>
       </c>
@@ -60061,13 +60056,13 @@
       <c r="G244" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H244" s="18">
+      <c r="H244" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20" t="s">
         <v>318</v>
       </c>
@@ -60090,13 +60085,13 @@
       <c r="G245" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H245" s="18">
+      <c r="H245" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20" t="s">
         <v>318</v>
       </c>
@@ -60118,13 +60113,13 @@
       <c r="G246" s="19">
         <v>0.75</v>
       </c>
-      <c r="H246" s="18">
+      <c r="H246" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20" t="s">
         <v>318</v>
       </c>
@@ -60146,13 +60141,13 @@
       <c r="G247" s="19">
         <v>0.75</v>
       </c>
-      <c r="H247" s="18">
+      <c r="H247" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20" t="s">
         <v>318</v>
       </c>
@@ -60174,13 +60169,13 @@
       <c r="G248" s="19">
         <v>0.75</v>
       </c>
-      <c r="H248" s="18">
+      <c r="H248" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20" t="s">
         <v>318</v>
       </c>
@@ -60203,13 +60198,13 @@
       <c r="G249" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H249" s="18">
+      <c r="H249" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20" t="s">
         <v>318</v>
       </c>
@@ -60232,13 +60227,13 @@
       <c r="G250" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H250" s="18">
+      <c r="H250" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20" t="s">
         <v>319</v>
       </c>
@@ -60261,13 +60256,13 @@
       <c r="G251" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H251" s="18">
+      <c r="H251" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20" t="s">
         <v>319</v>
       </c>
@@ -60290,13 +60285,13 @@
       <c r="G252" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H252" s="18">
+      <c r="H252" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20" t="s">
         <v>319</v>
       </c>
@@ -60319,13 +60314,13 @@
       <c r="G253" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H253" s="18">
+      <c r="H253" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20" t="s">
         <v>319</v>
       </c>
@@ -60348,13 +60343,13 @@
       <c r="G254" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H254" s="18">
+      <c r="H254" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20" t="s">
         <v>319</v>
       </c>
@@ -60377,13 +60372,13 @@
       <c r="G255" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H255" s="18">
+      <c r="H255" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20" t="s">
         <v>319</v>
       </c>
@@ -60406,13 +60401,13 @@
       <c r="G256" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H256" s="18">
+      <c r="H256" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20" t="s">
         <v>319</v>
       </c>
@@ -60435,13 +60430,13 @@
       <c r="G257" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H257" s="18">
+      <c r="H257" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20" t="s">
         <v>319</v>
       </c>
@@ -60464,13 +60459,13 @@
       <c r="G258" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H258" s="18">
+      <c r="H258" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20" t="s">
         <v>319</v>
       </c>
@@ -60493,10 +60488,10 @@
       <c r="G259" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H259" s="18">
+      <c r="H259" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
@@ -60522,13 +60517,13 @@
       <c r="G260" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H260" s="18">
+      <c r="H260" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20" t="s">
         <v>319</v>
       </c>
@@ -60551,13 +60546,13 @@
       <c r="G261" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H261" s="18">
+      <c r="H261" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20" t="s">
         <v>319</v>
       </c>
@@ -60580,13 +60575,13 @@
       <c r="G262" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H262" s="18">
+      <c r="H262" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20" t="s">
         <v>319</v>
       </c>
@@ -60609,13 +60604,13 @@
       <c r="G263" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H263" s="18">
+      <c r="H263" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20" t="s">
         <v>319</v>
       </c>
@@ -60638,13 +60633,13 @@
       <c r="G264" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H264" s="18">
+      <c r="H264" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20" t="s">
         <v>319</v>
       </c>
@@ -60667,13 +60662,13 @@
       <c r="G265" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H265" s="18">
+      <c r="H265" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20" t="s">
         <v>319</v>
       </c>
@@ -60696,13 +60691,13 @@
       <c r="G266" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H266" s="18">
+      <c r="H266" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20" t="s">
         <v>319</v>
       </c>
@@ -60725,13 +60720,13 @@
       <c r="G267" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H267" s="18">
+      <c r="H267" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20" t="s">
         <v>319</v>
       </c>
@@ -60754,13 +60749,13 @@
       <c r="G268" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H268" s="18">
+      <c r="H268" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20" t="s">
         <v>319</v>
       </c>
@@ -60783,13 +60778,13 @@
       <c r="G269" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H269" s="18">
+      <c r="H269" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20" t="s">
         <v>319</v>
       </c>
@@ -60811,13 +60806,13 @@
       <c r="G270" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H270" s="18">
+      <c r="H270" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20" t="s">
         <v>319</v>
       </c>
@@ -60839,13 +60834,13 @@
       <c r="G271" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H271" s="18">
+      <c r="H271" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20" t="s">
         <v>319</v>
       </c>
@@ -60868,13 +60863,13 @@
       <c r="G272" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H272" s="18">
+      <c r="H272" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20" t="s">
         <v>319</v>
       </c>
@@ -60897,13 +60892,13 @@
       <c r="G273" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H273" s="18">
+      <c r="H273" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20" t="s">
         <v>319</v>
       </c>
@@ -60926,13 +60921,13 @@
       <c r="G274" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H274" s="18">
+      <c r="H274" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20" t="s">
         <v>319</v>
       </c>
@@ -60955,13 +60950,13 @@
       <c r="G275" s="19">
         <v>0.70833333333333326</v>
       </c>
-      <c r="H275" s="18">
+      <c r="H275" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20" t="s">
         <v>319</v>
       </c>
@@ -60984,13 +60979,13 @@
       <c r="G276" s="19">
         <v>0.625</v>
       </c>
-      <c r="H276" s="18">
+      <c r="H276" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20" t="s">
         <v>319</v>
       </c>
@@ -61013,13 +61008,13 @@
       <c r="G277" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H277" s="18">
+      <c r="H277" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20" t="s">
         <v>319</v>
       </c>
@@ -61042,13 +61037,13 @@
       <c r="G278" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H278" s="18">
+      <c r="H278" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20" t="s">
         <v>319</v>
       </c>
@@ -61071,13 +61066,13 @@
       <c r="G279" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H279" s="18">
+      <c r="H279" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="s">
         <v>319</v>
       </c>
@@ -61100,13 +61095,13 @@
       <c r="G280" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H280" s="18">
+      <c r="H280" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20" t="s">
         <v>319</v>
       </c>
@@ -61129,13 +61124,13 @@
       <c r="G281" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H281" s="18">
+      <c r="H281" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="s">
         <v>319</v>
       </c>
@@ -61158,13 +61153,13 @@
       <c r="G282" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H282" s="18">
+      <c r="H282" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20" t="s">
         <v>319</v>
       </c>
@@ -61187,13 +61182,13 @@
       <c r="G283" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H283" s="18">
+      <c r="H283" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20" t="s">
         <v>319</v>
       </c>
@@ -61216,16 +61211,16 @@
       <c r="G284" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H284" s="18">
+      <c r="H284" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
       <c r="J284" s="17" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20" t="s">
         <v>319</v>
       </c>
@@ -61248,13 +61243,13 @@
       <c r="G285" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H285" s="18">
+      <c r="H285" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="s">
         <v>319</v>
       </c>
@@ -61277,13 +61272,13 @@
       <c r="G286" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H286" s="18">
+      <c r="H286" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20" t="s">
         <v>319</v>
       </c>
@@ -61306,13 +61301,13 @@
       <c r="G287" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H287" s="18">
+      <c r="H287" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="s">
         <v>319</v>
       </c>
@@ -61335,13 +61330,13 @@
       <c r="G288" s="19">
         <v>0.625</v>
       </c>
-      <c r="H288" s="18">
+      <c r="H288" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20" t="s">
         <v>319</v>
       </c>
@@ -61364,13 +61359,13 @@
       <c r="G289" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H289" s="18">
+      <c r="H289" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20" t="s">
         <v>319</v>
       </c>
@@ -61393,13 +61388,13 @@
       <c r="G290" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H290" s="18">
+      <c r="H290" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20" t="s">
         <v>319</v>
       </c>
@@ -61422,13 +61417,13 @@
       <c r="G291" s="19">
         <v>0.4375</v>
       </c>
-      <c r="H291" s="18">
+      <c r="H291" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20" t="s">
         <v>319</v>
       </c>
@@ -61451,13 +61446,13 @@
       <c r="G292" s="19">
         <v>0.39583333333333337</v>
       </c>
-      <c r="H292" s="18">
+      <c r="H292" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20" t="s">
         <v>319</v>
       </c>
@@ -61480,13 +61475,13 @@
       <c r="G293" s="19">
         <v>0.625</v>
       </c>
-      <c r="H293" s="18">
+      <c r="H293" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20" t="s">
         <v>319</v>
       </c>
@@ -61509,10 +61504,10 @@
       <c r="G294" s="19">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H294" s="18">
+      <c r="H294" s="18" t="e">
         <f>COUNTIF([1]!Table1[Course
 Code],Table4[[#This Row],[Code]])</f>
-        <v>1</v>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
